--- a/Deal_Proposal_Template.xlsx
+++ b/Deal_Proposal_Template.xlsx
@@ -686,7 +686,7 @@
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,6 +708,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -983,36 +990,80 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1020,51 +1071,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1072,19 +1083,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1096,27 +1103,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1218,7 +1229,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38160" y="114480"/>
+          <a:off x="38160" y="190440"/>
           <a:ext cx="304560" cy="304560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1240,9 +1251,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>456840</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>94680</xdr:rowOff>
+      <xdr:colOff>437760</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>56520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1255,8 +1266,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4127400" y="2076480"/>
-          <a:ext cx="418680" cy="418680"/>
+          <a:off x="3945240" y="4305240"/>
+          <a:ext cx="399600" cy="399600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1451,156 +1462,272 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:F27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="2.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.84"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="E7" s="6" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="E8" s="6" t="s">
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="6" t="s">
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+      <c r="B10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="E12" s="12" t="s">
+      <c r="C12" s="12"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="s">
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+      <c r="B13" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="F13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <f aca="false">C13</f>
         <v>0</v>
       </c>
-      <c r="F15" s="18"/>
-    </row>
-    <row r="16" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1"/>
+      <c r="B17" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
+      <c r="C18" s="12"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19" t="s">
+      <c r="C19" s="12"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="21" t="n">
         <f aca="false">C15+C17+C18+C19</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-    </row>
-    <row r="25" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="22" t="s">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1"/>
+      <c r="B25" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="E25" s="22" t="s">
+      <c r="C25" s="23"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="22"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="23" t="s">
+      <c r="F25" s="23"/>
+    </row>
+    <row r="26" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1"/>
+      <c r="B27" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1619,8 +1746,8 @@
     <mergeCell ref="B27:F27"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1643,128 +1770,128 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="25"/>
+      <c r="B1" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="29"/>
+      <c r="B5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="32" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33" t="s">
+      <c r="A7" s="33"/>
+      <c r="B7" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="32" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32"/>
-      <c r="B9" s="33" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="34" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="29"/>
+      <c r="B11" s="30"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="32" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27"/>
-      <c r="B13" s="31" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="32" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="29"/>
+      <c r="B16" s="30"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="28" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="29"/>
+      <c r="B20" s="30"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="28" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="28" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>41</v>
       </c>
     </row>
